--- a/diseases/d203/2005-2009.xlsx
+++ b/diseases/d203/2005-2009.xlsx
@@ -5376,11 +5376,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_CCHF_ANNUAL</t>
@@ -5398,12 +5393,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5413,11 +5403,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5483,17 +5468,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5532,34 +5517,12 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Crimean-Congo haemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5567,64 +5530,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5632,27 +5537,17 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
         <v>1</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -5660,7 +5555,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -5680,7 +5575,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -5722,12 +5617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5752,12 +5647,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5771,7 +5666,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
+          <t>SER_AT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5791,7 +5686,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
+          <t>SER_AT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -5799,42 +5694,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5761,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5915,7 +5810,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_BE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5935,7 +5830,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_BE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -5943,42 +5838,42 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6010,12 +5905,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6049,17 +5944,17 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.08012808206825003</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_BG_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6079,7 +5974,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_BG_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -6092,7 +5987,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6112,7 +6007,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6154,12 +6049,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6193,17 +6088,17 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.08012808206825003</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_CCHF_ANNUAL</t>
+          <t>SER_CY_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6223,7 +6118,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_CCHF_ANNUAL</t>
+          <t>SER_CY_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6236,7 +6131,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6256,7 +6151,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6298,12 +6193,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6347,7 +6242,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_CCHF_ANNUAL</t>
+          <t>SER_CZ_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6367,7 +6262,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_CCHF_ANNUAL</t>
+          <t>SER_CZ_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6380,7 +6275,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6400,7 +6295,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6442,12 +6337,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6481,17 +6376,17 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.002471110158470688</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_CCHF_ANNUAL</t>
+          <t>SER_DE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6511,7 +6406,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_CCHF_ANNUAL</t>
+          <t>SER_DE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -6519,42 +6414,42 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6481,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6625,17 +6520,17 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.002471110158470688</v>
+        <v>0</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_EE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6655,7 +6550,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_EE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6663,42 +6558,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6625,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6779,7 +6674,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_ES_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6799,7 +6694,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_ES_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -6812,7 +6707,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6832,7 +6727,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6874,12 +6769,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6923,7 +6818,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_CCHF_ANNUAL</t>
+          <t>SER_FR_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6943,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_CCHF_ANNUAL</t>
+          <t>SER_FR_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -6956,7 +6851,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6976,7 +6871,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -7018,12 +6913,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7067,7 +6962,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_CCHF_ANNUAL</t>
+          <t>SER_GB_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7087,7 +6982,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_CCHF_ANNUAL</t>
+          <t>SER_GB_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -7100,7 +6995,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -7120,7 +7015,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -7162,12 +7057,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7211,7 +7106,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_CCHF_ANNUAL</t>
+          <t>SER_GR_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7231,7 +7126,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_CCHF_ANNUAL</t>
+          <t>SER_GR_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7244,7 +7139,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -7264,7 +7159,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -7306,12 +7201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7355,7 +7250,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_CCHF_ANNUAL</t>
+          <t>SER_HU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7375,7 +7270,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_CCHF_ANNUAL</t>
+          <t>SER_HU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -7388,7 +7283,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -7408,7 +7303,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -7450,12 +7345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7499,7 +7394,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7519,7 +7414,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -7527,42 +7422,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -7594,12 +7489,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7643,7 +7538,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IS_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7663,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IS_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7671,42 +7566,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7738,12 +7633,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7787,7 +7682,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7807,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_CCHF_ANNUAL</t>
+          <t>SER_IT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -7815,42 +7710,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7777,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7931,7 +7826,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7951,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -7964,7 +7859,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -7984,7 +7879,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -8026,12 +7921,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8075,7 +7970,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -8095,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8108,7 +8003,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -8128,7 +8023,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -8170,12 +8065,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8219,7 +8114,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LV_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8239,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LV_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8252,7 +8147,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -8272,7 +8167,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -8314,12 +8209,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8363,7 +8258,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_CCHF_ANNUAL</t>
+          <t>SER_MT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8383,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_CCHF_ANNUAL</t>
+          <t>SER_MT_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8396,7 +8291,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -8416,7 +8311,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -8458,12 +8353,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8507,7 +8402,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_NL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8527,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_CCHF_ANNUAL</t>
+          <t>SER_NL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8540,7 +8435,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -8560,7 +8455,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -8602,12 +8497,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8651,7 +8546,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_CCHF_ANNUAL</t>
+          <t>SER_NO_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8671,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_CCHF_ANNUAL</t>
+          <t>SER_NO_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8679,42 +8574,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -8746,12 +8641,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8795,7 +8690,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_CCHF_ANNUAL</t>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8815,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_CCHF_ANNUAL</t>
+          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -8823,42 +8718,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8785,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8939,7 +8834,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+          <t>SER_RO_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8959,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_CCHF_ANNUAL</t>
+          <t>SER_RO_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -8972,7 +8867,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -8992,7 +8887,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -9034,12 +8929,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9083,7 +8978,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -9103,7 +8998,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SE_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9111,42 +9006,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9073,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9227,7 +9122,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9247,7 +9142,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9255,42 +9150,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9322,12 +9217,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9369,14 +9264,9 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9391,27 +9281,17 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
+          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
         <v>1</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -9419,7 +9299,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -9439,7 +9319,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -9448,384 +9328,6 @@
         </is>
       </c>
       <c r="BC61" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>crimean-congo-hemorrhagic-fever</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>克里米亚-刚果出血热</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Crimean-Congo haemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV62" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB62" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC62" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>crimean-congo-hemorrhagic-fever</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>克里米亚-刚果出血热</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV63" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA63" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB63" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC63" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -9957,7 +9459,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -9977,7 +9479,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9987,7 +9489,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
